--- a/head-yaw-telemetry.xlsx
+++ b/head-yaw-telemetry.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11550" yWindow="2775" windowWidth="37275" windowHeight="17550" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14160" yWindow="2625" windowWidth="37275" windowHeight="17550" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -54,17 +54,22 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0020406B"/>
+      <color rgb="FF20406B"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <family val="3"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -82,7 +87,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0020406B"/>
+        <fgColor rgb="FF20406B"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,28 +116,28 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="FFBBBBBB"/>
       </left>
       <right style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="FFBBBBBB"/>
       </right>
       <top style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="FFBBBBBB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BBBBBB"/>
+        <color rgb="FFBBBBBB"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -142,6 +147,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -511,14 +520,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Head-Orientation Telemetry — Peak Yaw Deviation per Stimulus Presentation</t>
         </is>
@@ -531,8 +540,9 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="3"/>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1. Overview</t>
         </is>
@@ -548,20 +558,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(30 participants x 5 auditory stimuli). Participant IDs (ID1-ID30) correspond to the P-numbers used in the paper</t>
+          <t>(30 participants x 5 auditory stimuli). Participants are labeled P01-P30, matching the P-numbers used in the paper.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>(e.g., ID3 = P3).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -583,8 +587,9 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2. Measurement</t>
         </is>
@@ -653,135 +658,137 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="23"/>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>3. Column definitions</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Participant identifier (ID1-ID30). Corresponds to the paper's P-numbers (ID3 = P3).</t>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>participant</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Participant identifier (P01-P30), matching the P-numbers used in the paper.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>event_index</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Presentation order for that participant (1-5): which of the five stimuli this was.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>stimulus</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Stimulus type: PV, GB, HV, BC, or DC (see Section 5).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Presentation direction of the stimulus: L = left, R = right.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>baseline_yaw_deg</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Baseline yaw [deg]: mean horizontal head angle over the 5 s before onset.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="31" ht="27" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>peak_toward_sound_yaw_deg</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Primary measure [deg]: maximum deviation from baseline toward the sound direction within the 5 s after onset. Rotation toward the sound is positive. (This is the value reported in the paper.)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>peak_raw_yaw_deg</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Raw yaw [deg] at the moment of the peak, i.e., the absolute head angle before subtracting the baseline.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33" ht="27" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>peak_yaw_change_deg</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Change from baseline [deg] at the moment of the peak, without direction-based sign flip (left rotation negative, right rotation positive).</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>peak_relative_time_sec</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Time of the peak [s], measured from stimulus onset (within the 0-5 s response window).</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>4. Relationship between the three peak columns</t>
         </is>
@@ -822,13 +829,11 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Example (ID3, HV presented from the left): baseline = -2.28, peak_raw = -75.32,</t>
+          <t>Example (P03, HV presented from the left): baseline = -2.28, peak_raw = -75.32,</t>
         </is>
       </c>
     </row>
@@ -839,92 +844,93 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="45"/>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>5. Abbreviations</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Stimulus</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>PV</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Phone Vibration</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Glass Breaking</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>HV</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Human Voice</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>Baby Crying</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>DC</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Dependent Context (in-game line-clear sound presented when no line clears)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>L / R</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Left / Right presentation direction</t>
         </is>
@@ -932,6 +938,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -958,7 +965,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1005,7 +1012,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1040,7 +1047,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1075,7 +1082,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1110,7 +1117,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1145,7 +1152,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1180,7 +1187,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1215,7 +1222,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1250,7 +1257,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1285,7 +1292,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1320,7 +1327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1355,7 +1362,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1390,7 +1397,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1425,7 +1432,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1460,7 +1467,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1495,7 +1502,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1530,7 +1537,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1565,7 +1572,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1600,7 +1607,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1635,7 +1642,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1670,7 +1677,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1705,7 +1712,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1740,7 +1747,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1775,7 +1782,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1810,7 +1817,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1845,7 +1852,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1880,7 +1887,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1915,7 +1922,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1950,7 +1957,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1985,7 +1992,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2020,7 +2027,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2055,7 +2062,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2090,7 +2097,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2125,7 +2132,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2160,7 +2167,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2195,7 +2202,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2230,7 +2237,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2265,7 +2272,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2300,7 +2307,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2335,7 +2342,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2370,7 +2377,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2405,7 +2412,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2440,7 +2447,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2475,7 +2482,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2510,7 +2517,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2545,7 +2552,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2580,7 +2587,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2615,7 +2622,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2650,7 +2657,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2685,7 +2692,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2720,7 +2727,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2755,7 +2762,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2790,7 +2797,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2825,7 +2832,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2860,7 +2867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2895,7 +2902,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2930,7 +2937,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2965,7 +2972,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3000,7 +3007,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3035,7 +3042,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3070,7 +3077,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3105,7 +3112,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3140,7 +3147,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3175,7 +3182,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3210,7 +3217,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -3245,7 +3252,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -3280,7 +3287,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -3315,7 +3322,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -3350,7 +3357,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -3385,7 +3392,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -3420,7 +3427,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -3455,7 +3462,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3490,7 +3497,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3525,7 +3532,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3560,7 +3567,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3595,7 +3602,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3630,7 +3637,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3665,7 +3672,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3700,7 +3707,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3735,7 +3742,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -3770,7 +3777,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3805,7 +3812,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3840,7 +3847,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3875,7 +3882,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3910,7 +3917,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3945,7 +3952,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3980,7 +3987,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -4015,7 +4022,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -4050,7 +4057,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4085,7 +4092,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -4120,7 +4127,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -4155,7 +4162,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -4190,7 +4197,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -4225,7 +4232,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -4260,7 +4267,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -4295,7 +4302,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -4330,7 +4337,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -4365,7 +4372,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -4400,7 +4407,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -4435,7 +4442,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -4470,7 +4477,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -4505,7 +4512,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -4540,7 +4547,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -4575,7 +4582,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4610,7 +4617,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -4645,7 +4652,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -4680,7 +4687,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -4715,7 +4722,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -4750,7 +4757,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -4785,7 +4792,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4820,7 +4827,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -4855,7 +4862,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -4890,7 +4897,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -4925,7 +4932,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -4960,7 +4967,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -4995,7 +5002,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -5030,7 +5037,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -5065,7 +5072,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -5100,7 +5107,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -5135,7 +5142,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -5170,7 +5177,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -5205,7 +5212,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -5240,7 +5247,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -5275,7 +5282,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -5310,7 +5317,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -5345,7 +5352,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -5380,7 +5387,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -5415,7 +5422,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -5450,7 +5457,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -5485,7 +5492,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -5520,7 +5527,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -5555,7 +5562,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -5590,7 +5597,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -5625,7 +5632,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -5660,7 +5667,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -5695,7 +5702,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -5730,7 +5737,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5765,7 +5772,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5800,7 +5807,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -5835,7 +5842,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -5870,7 +5877,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -5905,7 +5912,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -5940,7 +5947,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5975,7 +5982,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -6010,7 +6017,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -6045,7 +6052,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -6080,7 +6087,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -6115,7 +6122,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -6150,7 +6157,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -6185,7 +6192,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -6220,7 +6227,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -6252,20 +6259,23 @@
         <v>4.980199999999968</v>
       </c>
     </row>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
     <row r="155">
-      <c r="F155" s="8" t="n"/>
+      <c r="F155" s="9" t="n"/>
     </row>
     <row r="156">
-      <c r="F156" s="8" t="n"/>
+      <c r="F156" s="9" t="n"/>
     </row>
     <row r="157">
-      <c r="F157" s="8" t="n"/>
+      <c r="F157" s="9" t="n"/>
     </row>
     <row r="158">
-      <c r="F158" s="8" t="n"/>
+      <c r="F158" s="9" t="n"/>
     </row>
     <row r="159">
-      <c r="F159" s="8" t="n"/>
+      <c r="F159" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6295,7 +6305,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -6342,7 +6352,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -6377,7 +6387,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -6412,7 +6422,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6447,7 +6457,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6482,7 +6492,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6517,7 +6527,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6552,7 +6562,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6587,7 +6597,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6622,7 +6632,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6657,7 +6667,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6692,7 +6702,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6727,7 +6737,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6762,7 +6772,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6797,7 +6807,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6832,7 +6842,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6867,7 +6877,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6902,7 +6912,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6937,7 +6947,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6972,7 +6982,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -7007,7 +7017,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -7042,7 +7052,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -7077,7 +7087,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7112,7 +7122,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -7147,7 +7157,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7182,7 +7192,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -7217,7 +7227,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -7252,7 +7262,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -7287,7 +7297,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -7322,7 +7332,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7357,7 +7367,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7389,20 +7399,31 @@
         <v>3.073100000000011</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43">
-      <c r="F43" s="8" t="n"/>
+      <c r="F43" s="9" t="n"/>
     </row>
     <row r="44">
-      <c r="F44" s="8" t="n"/>
+      <c r="F44" s="9" t="n"/>
     </row>
     <row r="45">
-      <c r="F45" s="8" t="n"/>
+      <c r="F45" s="9" t="n"/>
     </row>
     <row r="46">
-      <c r="F46" s="8" t="n"/>
+      <c r="F46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7432,7 +7453,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -7479,7 +7500,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -7514,7 +7535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7549,7 +7570,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -7584,7 +7605,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7619,7 +7640,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7654,7 +7675,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7689,7 +7710,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7724,7 +7745,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7759,7 +7780,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7794,7 +7815,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -7829,7 +7850,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -7864,7 +7885,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -7899,7 +7920,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -7934,7 +7955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7969,7 +7990,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -8004,7 +8025,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -8039,7 +8060,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -8074,7 +8095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -8109,7 +8130,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -8144,7 +8165,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -8179,7 +8200,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -8214,7 +8235,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -8249,7 +8270,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -8284,7 +8305,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -8319,7 +8340,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -8354,7 +8375,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -8389,7 +8410,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -8424,7 +8445,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -8459,7 +8480,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -8494,7 +8515,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -8526,20 +8547,33 @@
         <v>2.724400000000003</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
     <row r="45">
-      <c r="F45" s="8" t="n"/>
+      <c r="F45" s="9" t="n"/>
     </row>
     <row r="46">
-      <c r="F46" s="8" t="n"/>
+      <c r="F46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="9" t="n"/>
     </row>
     <row r="48">
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8568,7 +8602,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -8615,7 +8649,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -8650,7 +8684,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -8685,7 +8719,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -8720,7 +8754,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -8755,7 +8789,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -8790,7 +8824,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -8825,7 +8859,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -8860,7 +8894,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -8895,7 +8929,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -8930,7 +8964,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -8965,7 +8999,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -9000,7 +9034,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -9035,7 +9069,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -9070,7 +9104,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -9105,7 +9139,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -9140,7 +9174,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -9175,7 +9209,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -9210,7 +9244,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -9245,7 +9279,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -9280,7 +9314,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -9315,7 +9349,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -9350,7 +9384,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -9385,7 +9419,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -9420,7 +9454,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -9455,7 +9489,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -9490,7 +9524,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -9525,7 +9559,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -9560,7 +9594,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -9595,7 +9629,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -9630,7 +9664,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -9662,20 +9696,35 @@
         <v>4.980199999999968</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="9" t="n"/>
     </row>
     <row r="48">
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="9" t="n"/>
     </row>
     <row r="50">
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="9" t="n"/>
     </row>
     <row r="51">
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9705,7 +9754,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -9752,7 +9801,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -9787,7 +9836,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -9822,7 +9871,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -9857,7 +9906,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -9892,7 +9941,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -9927,7 +9976,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -9962,7 +10011,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -9997,7 +10046,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -10032,7 +10081,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -10067,7 +10116,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -10102,7 +10151,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -10137,7 +10186,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -10172,7 +10221,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -10207,7 +10256,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -10242,7 +10291,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -10277,7 +10326,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -10312,7 +10361,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -10347,7 +10396,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -10382,7 +10431,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -10417,7 +10466,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -10452,7 +10501,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -10487,7 +10536,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -10522,7 +10571,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -10557,7 +10606,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -10592,7 +10641,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -10627,7 +10676,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -10662,7 +10711,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -10697,7 +10746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -10732,7 +10781,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -10767,7 +10816,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -10799,20 +10848,35 @@
         <v>0.003799999999998249</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47">
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="9" t="n"/>
     </row>
     <row r="48">
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="9" t="n"/>
     </row>
     <row r="50">
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="9" t="n"/>
     </row>
     <row r="51">
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10842,7 +10906,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -10889,7 +10953,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ID1</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -10924,7 +10988,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ID2</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -10959,7 +11023,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ID3</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -10994,7 +11058,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ID4</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -11029,7 +11093,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ID5</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -11064,7 +11128,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ID6</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -11099,7 +11163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ID7</t>
+          <t>P07</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -11134,7 +11198,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ID8</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -11169,7 +11233,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ID9</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -11204,7 +11268,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ID10</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -11239,7 +11303,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ID11</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -11274,7 +11338,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ID12</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -11309,7 +11373,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ID13</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -11344,7 +11408,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ID14</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -11379,7 +11443,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ID15</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -11414,7 +11478,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ID16</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -11449,7 +11513,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ID17</t>
+          <t>P17</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -11484,7 +11548,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ID18</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -11519,7 +11583,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ID19</t>
+          <t>P19</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -11554,7 +11618,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ID20</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -11589,7 +11653,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ID21</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -11624,7 +11688,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ID22</t>
+          <t>P22</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -11659,7 +11723,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ID23</t>
+          <t>P23</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -11694,7 +11758,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ID24</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -11729,7 +11793,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ID25</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -11764,7 +11828,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ID26</t>
+          <t>P26</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -11799,7 +11863,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ID27</t>
+          <t>P27</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -11834,7 +11898,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ID28</t>
+          <t>P28</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -11869,7 +11933,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ID29</t>
+          <t>P29</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -11904,7 +11968,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ID30</t>
+          <t>P30</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -11936,20 +12000,36 @@
         <v>0.57650000000001</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48">
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="9" t="n"/>
     </row>
     <row r="50">
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="9" t="n"/>
     </row>
     <row r="51">
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="9" t="n"/>
     </row>
     <row r="52">
-      <c r="F52" s="8" t="n"/>
+      <c r="F52" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
